--- a/payment_forms/011_yoga_mat_customization_order_form--payment_forms.xlsx
+++ b/payment_forms/011_yoga_mat_customization_order_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -765,8 +765,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -794,12 +794,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'cotton'}</t>
+          <t>cotton</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Cotton'}</t>
+          <t>Cotton</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'rubber'}</t>
+          <t>rubber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Rubber'}</t>
+          <t>Rubber</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'pvc'}</t>
+          <t>pvc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'PVC'}</t>
+          <t>PVC</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'solid'}</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Solid'}</t>
+          <t>Solid</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'striped'}</t>
+          <t>striped</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Striped'}</t>
+          <t>Striped</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'polka_dots'}</t>
+          <t>polka_dots</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Polka Dots'}</t>
+          <t>Polka Dots</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'PayPal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
